--- a/Geometria Universal de los Elementos 3-6-9.xlsx
+++ b/Geometria Universal de los Elementos 3-6-9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOCUMENTOS\WILLIAM\Inventos\BASE MAESTRA\EL UNIVERSO\POSTULADOS\Geometría Universal de los Elementos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE34DBBA-79B6-459A-B3BE-92761807FBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BC3FCA-1AEB-400F-BB40-E522F94DD48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B4059F9A-0D44-4216-AE89-DB16CD733EE3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B4059F9A-0D44-4216-AE89-DB16CD733EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="3-6-9" sheetId="2" r:id="rId1"/>

--- a/Geometria Universal de los Elementos 3-6-9.xlsx
+++ b/Geometria Universal de los Elementos 3-6-9.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOCUMENTOS\WILLIAM\Inventos\BASE MAESTRA\EL UNIVERSO\POSTULADOS\Geometría Universal de los Elementos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BC3FCA-1AEB-400F-BB40-E522F94DD48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00833BD1-FA5D-4E6F-9D48-98714DE64D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B4059F9A-0D44-4216-AE89-DB16CD733EE3}"/>
   </bookViews>
   <sheets>
-    <sheet name="3-6-9" sheetId="2" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="4" r:id="rId2"/>
+    <sheet name="UGE" sheetId="2" r:id="rId1"/>
+    <sheet name="Raiz Digital" sheetId="4" r:id="rId2"/>
+    <sheet name="Girasol Quimico" sheetId="5" r:id="rId3"/>
+    <sheet name="Octavas" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="192">
   <si>
     <t>Si</t>
   </si>
@@ -477,12 +479,424 @@
   <si>
     <t>W.H. AMELINES</t>
   </si>
+  <si>
+    <t>RAIZ DIGITAL DE TODOS LOS NUMEROS QUIMICOS</t>
+  </si>
+  <si>
+    <t>Nivel (Nota)</t>
+  </si>
+  <si>
+    <t>Espectro Óptico</t>
+  </si>
+  <si>
+    <t>Frecuencia Solfeggio &amp; Elemento Químico</t>
+  </si>
+  <si>
+    <t>Las 7 Octavas (Contexto Toroidal Macroscópico)</t>
+  </si>
+  <si>
+    <t>Resonancia Biológica</t>
+  </si>
+  <si>
+    <t>Código Tesla</t>
+  </si>
+  <si>
+    <t>1 (DO)</t>
+  </si>
+  <si>
+    <t>Gónadas / Base de la columna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3+9+6 = 18 </t>
+  </si>
+  <si>
+    <t>2 (RE)</t>
+  </si>
+  <si>
+    <t>Sistema Sacro / Fuerza Vital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4+1+7 = 12 </t>
+  </si>
+  <si>
+    <t>3 (MI)</t>
+  </si>
+  <si>
+    <t>Plexo Solar / Procesamiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5+2+8 = 15 </t>
+  </si>
+  <si>
+    <t>4 (FA)</t>
+  </si>
+  <si>
+    <t>Corazón / Glándula Timo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6+3+9 = 18 </t>
+  </si>
+  <si>
+    <t>5 (SOL)</t>
+  </si>
+  <si>
+    <t>Garganta / Tiroides y ATP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7+4+1 = 12 </t>
+  </si>
+  <si>
+    <t>6 (LA)</t>
+  </si>
+  <si>
+    <t>Tercer Ojo / Glándula Pineal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8+5+2 = 15 </t>
+  </si>
+  <si>
+    <t>7 (SI)</t>
+  </si>
+  <si>
+    <t>Coronilla / Conexión Fractal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9+6+3 = 18 </t>
+  </si>
+  <si>
+    <r>
+      <t>Rojo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (400 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">396 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Hidrógeno (H)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Supercúmulo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Laniakea / Gran Atractor)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Naranja</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (480 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">417 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Oxígeno (O)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Galaxia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Vía Láctea / Sagitario A*)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Amarillo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (525 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">528 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Carbono (C)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Sistema Solar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Sol y planetas)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verde</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (560 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">639 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Nitrógeno (N)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. El Planeta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Condensador Material)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Azul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (625 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">741 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Fósforo (P)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Biocampo Humano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (El Observador)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Índigo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (700 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">852 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calcio (Ca)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. La Célula</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Membrana y núcleo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Violeta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (750 THz)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">963 Hz - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Silicio (Si)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. El Átomo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Límite de Planck / Uroboros)</t>
+    </r>
+  </si>
+  <si>
+    <t>Las Lineas verdes y rojas son las lineas parastiquias, notese la conexión entre los numeros iguales diagonales</t>
+  </si>
+  <si>
+    <t>Notese en la tabla de las 21 columnas, las secuencias de numeros 2,5,8 - 1,4,7 y 3,6,9 (Frecuencia Solfeggio)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,6 +1076,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -743,7 +1172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1111,11 +1540,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1404,27 +1874,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1487,6 +1936,54 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7283,7 +7780,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3362320" y="4052879"/>
+          <a:off x="3362320" y="4100504"/>
           <a:ext cx="1643072" cy="885818"/>
           <a:chOff x="3500433" y="6727023"/>
           <a:chExt cx="1643072" cy="1381118"/>
@@ -7471,7 +7968,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3350420" y="3250407"/>
+          <a:off x="3350420" y="3298032"/>
           <a:ext cx="3169464" cy="1681156"/>
           <a:chOff x="3488533" y="5429251"/>
           <a:chExt cx="3169464" cy="2681281"/>
@@ -7756,7 +8253,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10979913" y="3250402"/>
+          <a:off x="10979913" y="3298027"/>
           <a:ext cx="1643072" cy="885818"/>
           <a:chOff x="3500433" y="6727023"/>
           <a:chExt cx="1643072" cy="1381118"/>
@@ -7944,7 +8441,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4883944" y="3259935"/>
+          <a:off x="4883944" y="3307560"/>
           <a:ext cx="3169464" cy="1671631"/>
           <a:chOff x="3488533" y="5429251"/>
           <a:chExt cx="3169464" cy="2681281"/>
@@ -8229,7 +8726,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6405558" y="3248030"/>
+          <a:off x="6405558" y="3295655"/>
           <a:ext cx="3169464" cy="1690681"/>
           <a:chOff x="3488533" y="5429251"/>
           <a:chExt cx="3169464" cy="2681281"/>
@@ -8514,7 +9011,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7927169" y="3293277"/>
+          <a:off x="7927169" y="3340902"/>
           <a:ext cx="3169464" cy="1690681"/>
           <a:chOff x="3488533" y="5429251"/>
           <a:chExt cx="3169464" cy="2681281"/>
@@ -8799,7 +9296,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9470208" y="3243268"/>
+          <a:off x="9470208" y="3290893"/>
           <a:ext cx="3169464" cy="1681156"/>
           <a:chOff x="3488533" y="5429251"/>
           <a:chExt cx="3169464" cy="2681281"/>
@@ -9084,7 +9581,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1445906" y="1218416"/>
+          <a:off x="1445906" y="1266041"/>
           <a:ext cx="4688195" cy="893099"/>
           <a:chOff x="-4233905" y="2842098"/>
           <a:chExt cx="4361983" cy="1445148"/>
@@ -9321,7 +9818,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5265431" y="1208891"/>
+          <a:off x="5265431" y="1256516"/>
           <a:ext cx="4688195" cy="893099"/>
           <a:chOff x="-4233905" y="2842098"/>
           <a:chExt cx="4361983" cy="1445148"/>
@@ -9558,7 +10055,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9827906" y="1237466"/>
+          <a:off x="9827906" y="1285091"/>
           <a:ext cx="4688195" cy="893099"/>
           <a:chOff x="-4233905" y="2842098"/>
           <a:chExt cx="4361983" cy="1445148"/>
@@ -9767,6 +10264,696 @@
         </xdr:txBody>
       </xdr:sp>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>68970</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>178594</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D33DD9F4-4458-425A-9530-611AA009FF50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="219075" y="2450220"/>
+          <a:ext cx="2638425" cy="2709949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>223659</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>148538</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BD93D54-D45D-4882-ABE6-FC17B697EC64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13573125" y="2343150"/>
+          <a:ext cx="2252484" cy="2786963"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68C880F8-7ACA-6D45-76CD-7E287878CB60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="219075" y="57150"/>
+          <a:ext cx="11601450" cy="11772900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3EBA5A8-402A-373D-73C2-AF58CA8E4343}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="1571625"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6767B3FA-E25F-9EEA-8F19-4D9CAA795EE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="2085975"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D252523-7F6D-EA8D-041D-F2C3A5CF28EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="2600325"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F26B369-C1A4-0ACF-E86B-FAEDD11E2EC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="3114675"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FA9D1A6-1FF1-52C0-84AF-3FFBFD714B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="3629025"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E4CD6E2-8F93-19A2-0D2F-D43A4DFC97E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="4143375"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15277E55-6CA8-ABC3-26CC-537585DAE112}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4572000" y="4829175"/>
+          <a:ext cx="85725" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10092,7 +11279,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:BA59"/>
+  <dimension ref="B3:BB59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
@@ -10106,50 +11293,50 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:48" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="123" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
-      <c r="T3" s="103"/>
-      <c r="U3" s="103"/>
-      <c r="V3" s="103"/>
-      <c r="W3" s="103"/>
-      <c r="X3" s="103"/>
-      <c r="Y3" s="103"/>
-      <c r="Z3" s="103"/>
-      <c r="AA3" s="103"/>
-      <c r="AB3" s="103"/>
-      <c r="AC3" s="103"/>
-      <c r="AD3" s="103"/>
-      <c r="AE3" s="103"/>
-      <c r="AF3" s="103"/>
-      <c r="AG3" s="103"/>
-      <c r="AH3" s="103"/>
-      <c r="AI3" s="103"/>
-      <c r="AJ3" s="103"/>
-      <c r="AK3" s="103"/>
-      <c r="AL3" s="103"/>
-      <c r="AM3" s="103"/>
-      <c r="AN3" s="103"/>
-      <c r="AO3" s="103"/>
-      <c r="AP3" s="103"/>
-      <c r="AQ3" s="103"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="123"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="123"/>
+      <c r="AD3" s="123"/>
+      <c r="AE3" s="123"/>
+      <c r="AF3" s="123"/>
+      <c r="AG3" s="123"/>
+      <c r="AH3" s="123"/>
+      <c r="AI3" s="123"/>
+      <c r="AJ3" s="123"/>
+      <c r="AK3" s="123"/>
+      <c r="AL3" s="123"/>
+      <c r="AM3" s="123"/>
+      <c r="AN3" s="123"/>
+      <c r="AO3" s="123"/>
+      <c r="AP3" s="123"/>
+      <c r="AQ3" s="123"/>
     </row>
     <row r="5" spans="2:48" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:48" s="7" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10410,95 +11597,95 @@
     </row>
     <row r="9" spans="2:48" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:48" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="100">
+      <c r="B10" s="119">
         <v>1</v>
       </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="98">
+      <c r="C10" s="120"/>
+      <c r="D10" s="121">
         <v>2</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="100">
+      <c r="E10" s="122"/>
+      <c r="F10" s="119">
         <v>3</v>
       </c>
-      <c r="G10" s="101"/>
-      <c r="H10" s="98">
+      <c r="G10" s="120"/>
+      <c r="H10" s="121">
         <v>4</v>
       </c>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100">
+      <c r="I10" s="122"/>
+      <c r="J10" s="119">
         <v>5</v>
       </c>
-      <c r="K10" s="101"/>
-      <c r="L10" s="98">
+      <c r="K10" s="120"/>
+      <c r="L10" s="121">
         <v>6</v>
       </c>
-      <c r="M10" s="99"/>
-      <c r="N10" s="100">
+      <c r="M10" s="122"/>
+      <c r="N10" s="119">
         <v>7</v>
       </c>
-      <c r="O10" s="101"/>
-      <c r="P10" s="98">
+      <c r="O10" s="120"/>
+      <c r="P10" s="121">
         <v>8</v>
       </c>
-      <c r="Q10" s="99"/>
-      <c r="R10" s="100">
+      <c r="Q10" s="122"/>
+      <c r="R10" s="119">
         <v>9</v>
       </c>
-      <c r="S10" s="101"/>
-      <c r="T10" s="98">
+      <c r="S10" s="120"/>
+      <c r="T10" s="121">
         <v>10</v>
       </c>
-      <c r="U10" s="99"/>
-      <c r="V10" s="100">
+      <c r="U10" s="122"/>
+      <c r="V10" s="119">
         <v>11</v>
       </c>
-      <c r="W10" s="101"/>
-      <c r="X10" s="98">
+      <c r="W10" s="120"/>
+      <c r="X10" s="121">
         <v>12</v>
       </c>
-      <c r="Y10" s="99"/>
-      <c r="Z10" s="100">
+      <c r="Y10" s="122"/>
+      <c r="Z10" s="119">
         <v>13</v>
       </c>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="100">
+      <c r="AA10" s="120"/>
+      <c r="AB10" s="119">
         <v>14</v>
       </c>
-      <c r="AC10" s="101"/>
-      <c r="AD10" s="98">
+      <c r="AC10" s="120"/>
+      <c r="AD10" s="121">
         <v>15</v>
       </c>
-      <c r="AE10" s="99"/>
-      <c r="AF10" s="100">
+      <c r="AE10" s="122"/>
+      <c r="AF10" s="119">
         <v>16</v>
       </c>
-      <c r="AG10" s="101"/>
-      <c r="AH10" s="100">
+      <c r="AG10" s="120"/>
+      <c r="AH10" s="119">
         <v>17</v>
       </c>
-      <c r="AI10" s="101"/>
-      <c r="AJ10" s="98">
+      <c r="AI10" s="120"/>
+      <c r="AJ10" s="121">
         <v>18</v>
       </c>
-      <c r="AK10" s="99"/>
-      <c r="AL10" s="100">
+      <c r="AK10" s="122"/>
+      <c r="AL10" s="119">
         <v>19</v>
       </c>
-      <c r="AM10" s="101"/>
-      <c r="AN10" s="100">
+      <c r="AM10" s="120"/>
+      <c r="AN10" s="119">
         <v>20</v>
       </c>
-      <c r="AO10" s="101"/>
-      <c r="AP10" s="98">
+      <c r="AO10" s="120"/>
+      <c r="AP10" s="121">
         <v>21</v>
       </c>
-      <c r="AQ10" s="101"/>
-      <c r="AR10" s="104" t="s">
+      <c r="AQ10" s="120"/>
+      <c r="AR10" s="124" t="s">
         <v>124</v>
       </c>
-      <c r="AS10" s="104"/>
-      <c r="AT10" s="104"/>
+      <c r="AS10" s="124"/>
+      <c r="AT10" s="124"/>
     </row>
     <row r="11" spans="2:48" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="12" t="s">
@@ -11337,7 +12524,7 @@
       </c>
       <c r="AV16" s="7"/>
     </row>
-    <row r="17" spans="2:53" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:54" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="63">
         <v>2</v>
       </c>
@@ -11479,12 +12666,12 @@
       </c>
       <c r="AV17" s="7"/>
     </row>
-    <row r="18" spans="2:53" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:54" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AS18" s="25"/>
       <c r="AT18" s="25"/>
       <c r="AU18" s="25"/>
     </row>
-    <row r="19" spans="2:53" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:54" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="V19" s="5">
         <v>1</v>
       </c>
@@ -11492,7 +12679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:53" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:54" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V20" s="16" t="s">
         <v>14</v>
       </c>
@@ -11500,7 +12687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:53" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:54" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V21" s="18">
         <v>1</v>
       </c>
@@ -11508,9 +12695,10 @@
         <v>13</v>
       </c>
       <c r="BA21"/>
+      <c r="BB21"/>
     </row>
-    <row r="22" spans="2:53" s="11" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:53" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:54" s="11" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:54" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J23" s="37">
         <v>2</v>
       </c>
@@ -11602,11 +12790,11 @@
       <c r="AM23" s="27">
         <v>5</v>
       </c>
-      <c r="AN23" s="102">
+      <c r="AN23" s="125">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="2:53" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:54" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J24" s="45">
         <v>15</v>
       </c>
@@ -11698,12 +12886,12 @@
       <c r="AM24" s="28">
         <v>3</v>
       </c>
-      <c r="AN24" s="102"/>
+      <c r="AN24" s="125"/>
       <c r="AO24" s="8">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="2:53" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:54" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J25" s="45">
         <v>28</v>
       </c>
@@ -11795,10 +12983,10 @@
       <c r="AM25" s="29">
         <v>1</v>
       </c>
-      <c r="AN25" s="102"/>
+      <c r="AN25" s="125"/>
       <c r="AO25" s="8"/>
     </row>
-    <row r="26" spans="2:53" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:54" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J26" s="45">
         <v>41</v>
       </c>
@@ -11890,12 +13078,12 @@
       <c r="AM26" s="33">
         <v>8</v>
       </c>
-      <c r="AN26" s="102">
+      <c r="AN26" s="125">
         <v>18</v>
       </c>
       <c r="AO26" s="8"/>
     </row>
-    <row r="27" spans="2:53" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:54" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J27" s="45">
         <v>54</v>
       </c>
@@ -11987,12 +13175,12 @@
       <c r="AM27" s="34">
         <v>6</v>
       </c>
-      <c r="AN27" s="102"/>
+      <c r="AN27" s="125"/>
       <c r="AO27" s="8">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="2:53" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:54" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J28" s="45">
         <v>67</v>
       </c>
@@ -12084,10 +13272,10 @@
       <c r="AM28" s="35">
         <v>4</v>
       </c>
-      <c r="AN28" s="102"/>
+      <c r="AN28" s="125"/>
       <c r="AO28" s="8"/>
     </row>
-    <row r="29" spans="2:53" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:54" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J29" s="45">
         <v>80</v>
       </c>
@@ -12179,12 +13367,12 @@
       <c r="AM29" s="30">
         <v>2</v>
       </c>
-      <c r="AN29" s="102">
+      <c r="AN29" s="125">
         <v>18</v>
       </c>
       <c r="AO29" s="8"/>
     </row>
-    <row r="30" spans="2:53" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:54" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J30" s="45">
         <v>93</v>
       </c>
@@ -12276,12 +13464,12 @@
       <c r="AM30" s="31">
         <v>9</v>
       </c>
-      <c r="AN30" s="102"/>
+      <c r="AN30" s="125"/>
       <c r="AO30" s="8">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="2:53" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:54" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J31" s="63">
         <v>106</v>
       </c>
@@ -12373,61 +13561,61 @@
       <c r="AM31" s="32">
         <v>7</v>
       </c>
-      <c r="AN31" s="102"/>
+      <c r="AN31" s="125"/>
     </row>
-    <row r="32" spans="2:53" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="J32" s="100">
+    <row r="32" spans="2:54" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J32" s="119">
         <v>1</v>
       </c>
-      <c r="K32" s="101"/>
-      <c r="L32" s="98">
+      <c r="K32" s="120"/>
+      <c r="L32" s="121">
         <v>2</v>
       </c>
-      <c r="M32" s="99"/>
-      <c r="N32" s="100">
+      <c r="M32" s="122"/>
+      <c r="N32" s="119">
         <v>3</v>
       </c>
-      <c r="O32" s="101"/>
-      <c r="P32" s="98">
+      <c r="O32" s="120"/>
+      <c r="P32" s="121">
         <v>4</v>
       </c>
-      <c r="Q32" s="99"/>
-      <c r="R32" s="100">
+      <c r="Q32" s="122"/>
+      <c r="R32" s="119">
         <v>5</v>
       </c>
-      <c r="S32" s="101"/>
-      <c r="T32" s="98">
+      <c r="S32" s="120"/>
+      <c r="T32" s="121">
         <v>6</v>
       </c>
-      <c r="U32" s="99"/>
-      <c r="V32" s="100">
+      <c r="U32" s="122"/>
+      <c r="V32" s="119">
         <v>7</v>
       </c>
-      <c r="W32" s="101"/>
-      <c r="X32" s="98">
+      <c r="W32" s="120"/>
+      <c r="X32" s="121">
         <v>8</v>
       </c>
-      <c r="Y32" s="99"/>
-      <c r="Z32" s="100">
+      <c r="Y32" s="122"/>
+      <c r="Z32" s="119">
         <v>9</v>
       </c>
-      <c r="AA32" s="101"/>
-      <c r="AB32" s="98">
+      <c r="AA32" s="120"/>
+      <c r="AB32" s="121">
         <v>10</v>
       </c>
-      <c r="AC32" s="99"/>
-      <c r="AD32" s="100">
+      <c r="AC32" s="122"/>
+      <c r="AD32" s="119">
         <v>11</v>
       </c>
-      <c r="AE32" s="101"/>
-      <c r="AF32" s="98">
+      <c r="AE32" s="120"/>
+      <c r="AF32" s="121">
         <v>12</v>
       </c>
-      <c r="AG32" s="99"/>
-      <c r="AH32" s="100">
+      <c r="AG32" s="122"/>
+      <c r="AH32" s="119">
         <v>13</v>
       </c>
-      <c r="AI32" s="101"/>
+      <c r="AI32" s="120"/>
     </row>
     <row r="33" spans="2:47" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J33" s="12" t="s">
@@ -12508,23 +13696,23 @@
       <c r="AI33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AJ33" s="104" t="s">
+      <c r="AJ33" s="124" t="s">
         <v>125</v>
       </c>
-      <c r="AK33" s="104"/>
-      <c r="AL33" s="104"/>
+      <c r="AK33" s="124"/>
+      <c r="AL33" s="124"/>
     </row>
     <row r="34" spans="2:47" s="1" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="2:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="100" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="107"/>
-      <c r="H35" s="107"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
       <c r="J35" s="9">
         <f>SUM(J23:J31)</f>
         <v>486</v>
@@ -12592,13 +13780,13 @@
       <c r="AI35" s="8"/>
     </row>
     <row r="36" spans="2:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="107"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
-      <c r="F36" s="107"/>
-      <c r="G36" s="107"/>
-      <c r="H36" s="107"/>
+      <c r="B36" s="100"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
       <c r="J36" s="2">
         <v>18</v>
       </c>
@@ -12650,26 +13838,26 @@
       <c r="AH36" s="2">
         <v>18</v>
       </c>
-      <c r="AO36" s="105" t="s">
+      <c r="AO36" s="98" t="s">
         <v>122</v>
       </c>
-      <c r="AP36" s="105"/>
-      <c r="AQ36" s="105" t="s">
+      <c r="AP36" s="98"/>
+      <c r="AQ36" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="AR36" s="105"/>
-      <c r="AS36" s="105"/>
-      <c r="AT36" s="105"/>
-      <c r="AU36" s="105"/>
+      <c r="AR36" s="98"/>
+      <c r="AS36" s="98"/>
+      <c r="AT36" s="98"/>
+      <c r="AU36" s="98"/>
     </row>
     <row r="37" spans="2:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="107"/>
-      <c r="C37" s="107"/>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="107"/>
-      <c r="G37" s="107"/>
-      <c r="H37" s="107"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
       <c r="J37" s="10">
         <v>9</v>
       </c>
@@ -12722,109 +13910,108 @@
         <v>9</v>
       </c>
       <c r="AM37" s="36"/>
-      <c r="AO37" s="122" t="s">
+      <c r="AO37" s="115" t="s">
         <v>137</v>
       </c>
-      <c r="AP37" s="122"/>
-      <c r="AQ37" s="122" t="s">
+      <c r="AP37" s="115"/>
+      <c r="AQ37" s="115" t="s">
         <v>136</v>
       </c>
-      <c r="AR37" s="122"/>
-      <c r="AS37" s="122"/>
-      <c r="AT37" s="122"/>
-      <c r="AU37" s="122"/>
+      <c r="AR37" s="115"/>
+      <c r="AS37" s="115"/>
+      <c r="AT37" s="115"/>
+      <c r="AU37" s="115"/>
     </row>
     <row r="40" spans="2:47" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="108" t="s">
+      <c r="B40" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="113" t="s">
+      <c r="F40" s="106" t="s">
         <v>128</v>
       </c>
-      <c r="G40" s="114"/>
-      <c r="H40" s="114"/>
-      <c r="I40" s="115"/>
+      <c r="G40" s="107"/>
+      <c r="H40" s="107"/>
+      <c r="I40" s="108"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="116" t="s">
+      <c r="K40" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="L40" s="117"/>
-      <c r="M40" s="117"/>
-      <c r="N40" s="118"/>
+      <c r="L40" s="110"/>
+      <c r="M40" s="110"/>
+      <c r="N40" s="111"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="109" t="s">
+      <c r="P40" s="102" t="s">
         <v>130</v>
       </c>
-      <c r="Q40" s="110"/>
-      <c r="R40" s="110"/>
-      <c r="S40" s="111"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="103"/>
+      <c r="S40" s="104"/>
       <c r="T40" s="4"/>
-      <c r="U40" s="119" t="s">
+      <c r="U40" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="V40" s="120"/>
-      <c r="W40" s="121"/>
+      <c r="V40" s="113"/>
+      <c r="W40" s="114"/>
       <c r="X40" s="4"/>
-      <c r="Y40" s="106" t="s">
+      <c r="Y40" s="99" t="s">
         <v>126</v>
       </c>
-      <c r="Z40" s="106"/>
-      <c r="AA40" s="106"/>
-      <c r="AB40" s="106"/>
+      <c r="Z40" s="99"/>
+      <c r="AA40" s="99"/>
+      <c r="AB40" s="99"/>
       <c r="AC40" s="4"/>
-      <c r="AD40" s="123" t="s">
+      <c r="AD40" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="AE40" s="123"/>
-      <c r="AF40" s="123"/>
-      <c r="AG40" s="123"/>
+      <c r="AE40" s="116"/>
+      <c r="AF40" s="116"/>
+      <c r="AG40" s="116"/>
       <c r="AH40" s="4"/>
-      <c r="AI40" s="124" t="s">
+      <c r="AI40" s="117" t="s">
         <v>133</v>
       </c>
-      <c r="AJ40" s="124"/>
-      <c r="AK40" s="124"/>
-      <c r="AL40" s="124"/>
+      <c r="AJ40" s="117"/>
+      <c r="AK40" s="117"/>
+      <c r="AL40" s="117"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="125" t="s">
+      <c r="AN40" s="118" t="s">
         <v>134</v>
       </c>
-      <c r="AO40" s="125"/>
-      <c r="AP40" s="125"/>
-      <c r="AR40" s="112" t="s">
+      <c r="AO40" s="118"/>
+      <c r="AP40" s="118"/>
+      <c r="AR40" s="105" t="s">
         <v>135</v>
       </c>
-      <c r="AS40" s="112"/>
-      <c r="AT40" s="112"/>
-      <c r="AU40" s="112"/>
+      <c r="AS40" s="105"/>
+      <c r="AT40" s="105"/>
+      <c r="AU40" s="105"/>
     </row>
     <row r="53" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="59" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="AQ36:AU36"/>
-    <mergeCell ref="AO36:AP36"/>
-    <mergeCell ref="Y40:AB40"/>
-    <mergeCell ref="B35:H37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="P40:S40"/>
-    <mergeCell ref="AR40:AU40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="U40:W40"/>
-    <mergeCell ref="AQ37:AU37"/>
-    <mergeCell ref="AO37:AP37"/>
-    <mergeCell ref="AD40:AG40"/>
-    <mergeCell ref="AI40:AL40"/>
-    <mergeCell ref="AN40:AP40"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AF32:AG32"/>
-    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="AP10:AQ10"/>
+    <mergeCell ref="AN23:AN25"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="AB10:AC10"/>
+    <mergeCell ref="AD10:AE10"/>
+    <mergeCell ref="AF10:AG10"/>
+    <mergeCell ref="AH10:AI10"/>
     <mergeCell ref="B3:AQ3"/>
     <mergeCell ref="AJ33:AL33"/>
     <mergeCell ref="AR10:AT10"/>
@@ -12841,25 +14028,26 @@
     <mergeCell ref="AJ10:AK10"/>
     <mergeCell ref="AL10:AM10"/>
     <mergeCell ref="AN10:AO10"/>
-    <mergeCell ref="AP10:AQ10"/>
-    <mergeCell ref="AN23:AN25"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="AB10:AC10"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="AF10:AG10"/>
-    <mergeCell ref="AH10:AI10"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AF32:AG32"/>
+    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="AQ36:AU36"/>
+    <mergeCell ref="AO36:AP36"/>
+    <mergeCell ref="Y40:AB40"/>
+    <mergeCell ref="B35:H37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="P40:S40"/>
+    <mergeCell ref="AR40:AU40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="U40:W40"/>
+    <mergeCell ref="AQ37:AU37"/>
+    <mergeCell ref="AO37:AP37"/>
+    <mergeCell ref="AD40:AG40"/>
+    <mergeCell ref="AI40:AL40"/>
+    <mergeCell ref="AN40:AP40"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.19685039370078741" bottom="0.15748031496062992" header="0.11811023622047245" footer="0.11811023622047245"/>
@@ -12873,99 +14061,145 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C69D4F-207F-45E7-AB45-7C0F959456E5}">
-  <dimension ref="B3:AQ26"/>
+  <dimension ref="B2:AQ30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="43" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:43" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B2" s="133" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="133"/>
+      <c r="S2" s="133"/>
+      <c r="T2" s="133"/>
+      <c r="U2" s="133"/>
+      <c r="V2" s="133"/>
+      <c r="W2" s="133"/>
+      <c r="X2" s="133"/>
+      <c r="Y2" s="133"/>
+      <c r="Z2" s="133"/>
+      <c r="AA2" s="133"/>
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="133"/>
+      <c r="AD2" s="133"/>
+      <c r="AE2" s="133"/>
+      <c r="AF2" s="133"/>
+      <c r="AG2" s="133"/>
+      <c r="AH2" s="133"/>
+      <c r="AI2" s="133"/>
+      <c r="AJ2" s="133"/>
+      <c r="AK2" s="133"/>
+      <c r="AL2" s="133"/>
+      <c r="AM2" s="133"/>
+      <c r="AN2" s="133"/>
+      <c r="AO2" s="133"/>
+      <c r="AP2" s="133"/>
+      <c r="AQ2" s="133"/>
+    </row>
     <row r="3" spans="2:43" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:43" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="100">
+      <c r="B4" s="119">
         <v>1</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="98">
+      <c r="C4" s="120"/>
+      <c r="D4" s="121">
         <v>2</v>
       </c>
-      <c r="E4" s="99"/>
-      <c r="F4" s="100">
+      <c r="E4" s="122"/>
+      <c r="F4" s="119">
         <v>3</v>
       </c>
-      <c r="G4" s="101"/>
-      <c r="H4" s="98">
+      <c r="G4" s="120"/>
+      <c r="H4" s="121">
         <v>4</v>
       </c>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100">
+      <c r="I4" s="122"/>
+      <c r="J4" s="119">
         <v>5</v>
       </c>
-      <c r="K4" s="101"/>
-      <c r="L4" s="98">
+      <c r="K4" s="120"/>
+      <c r="L4" s="121">
         <v>6</v>
       </c>
-      <c r="M4" s="99"/>
-      <c r="N4" s="100">
+      <c r="M4" s="122"/>
+      <c r="N4" s="119">
         <v>7</v>
       </c>
-      <c r="O4" s="101"/>
-      <c r="P4" s="98">
+      <c r="O4" s="120"/>
+      <c r="P4" s="121">
         <v>8</v>
       </c>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="100">
+      <c r="Q4" s="122"/>
+      <c r="R4" s="119">
         <v>9</v>
       </c>
-      <c r="S4" s="101"/>
-      <c r="T4" s="98">
+      <c r="S4" s="120"/>
+      <c r="T4" s="121">
         <v>10</v>
       </c>
-      <c r="U4" s="99"/>
-      <c r="V4" s="100">
+      <c r="U4" s="122"/>
+      <c r="V4" s="119">
         <v>11</v>
       </c>
-      <c r="W4" s="101"/>
-      <c r="X4" s="98">
+      <c r="W4" s="120"/>
+      <c r="X4" s="121">
         <v>12</v>
       </c>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="100">
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="119">
         <v>13</v>
       </c>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="100">
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="119">
         <v>14</v>
       </c>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="98">
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121">
         <v>15</v>
       </c>
-      <c r="AE4" s="99"/>
-      <c r="AF4" s="100">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="119">
         <v>16</v>
       </c>
-      <c r="AG4" s="101"/>
-      <c r="AH4" s="100">
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="119">
         <v>17</v>
       </c>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="98">
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="121">
         <v>18</v>
       </c>
-      <c r="AK4" s="99"/>
-      <c r="AL4" s="100">
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="119">
         <v>19</v>
       </c>
-      <c r="AM4" s="101"/>
-      <c r="AN4" s="100">
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="119">
         <v>20</v>
       </c>
-      <c r="AO4" s="101"/>
-      <c r="AP4" s="98">
+      <c r="AO4" s="120"/>
+      <c r="AP4" s="121">
         <v>21</v>
       </c>
-      <c r="AQ4" s="101"/>
+      <c r="AQ4" s="120"/>
     </row>
     <row r="5" spans="2:43" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
@@ -13871,7 +15105,7 @@
       </c>
     </row>
     <row r="16" spans="2:43" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I17" s="37">
         <v>2</v>
       </c>
@@ -13951,7 +15185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I18" s="45">
         <v>6</v>
       </c>
@@ -14031,7 +15265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I19" s="45">
         <v>1</v>
       </c>
@@ -14111,7 +15345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I20" s="45">
         <v>5</v>
       </c>
@@ -14191,7 +15425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I21" s="45">
         <v>9</v>
       </c>
@@ -14271,7 +15505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I22" s="45">
         <v>4</v>
       </c>
@@ -14351,7 +15585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I23" s="45">
         <v>8</v>
       </c>
@@ -14431,7 +15665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I24" s="45">
         <v>3</v>
       </c>
@@ -14511,7 +15745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="9:34" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:34" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I25" s="63">
         <v>7</v>
       </c>
@@ -14591,18 +15825,148 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="9:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I26" s="119">
+        <v>1</v>
+      </c>
+      <c r="J26" s="120"/>
+      <c r="K26" s="121">
+        <v>2</v>
+      </c>
+      <c r="L26" s="122"/>
+      <c r="M26" s="119">
+        <v>3</v>
+      </c>
+      <c r="N26" s="120"/>
+      <c r="O26" s="121">
+        <v>4</v>
+      </c>
+      <c r="P26" s="122"/>
+      <c r="Q26" s="119">
+        <v>5</v>
+      </c>
+      <c r="R26" s="120"/>
+      <c r="S26" s="121">
+        <v>6</v>
+      </c>
+      <c r="T26" s="122"/>
+      <c r="U26" s="119">
+        <v>7</v>
+      </c>
+      <c r="V26" s="120"/>
+      <c r="W26" s="121">
+        <v>8</v>
+      </c>
+      <c r="X26" s="122"/>
+      <c r="Y26" s="119">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="120"/>
+      <c r="AA26" s="121">
+        <v>10</v>
+      </c>
+      <c r="AB26" s="122"/>
+      <c r="AC26" s="119">
+        <v>11</v>
+      </c>
+      <c r="AD26" s="120"/>
+      <c r="AE26" s="121">
+        <v>12</v>
+      </c>
+      <c r="AF26" s="122"/>
+      <c r="AG26" s="119">
+        <v>13</v>
+      </c>
+      <c r="AH26" s="120"/>
+    </row>
+    <row r="29" spans="4:34" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D29" s="134" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="134"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="134"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="134"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="134"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="134"/>
+      <c r="T29" s="134"/>
+      <c r="U29" s="134"/>
+      <c r="V29" s="134"/>
+      <c r="W29" s="134"/>
+      <c r="X29" s="134"/>
+      <c r="Y29" s="134"/>
+      <c r="Z29" s="134"/>
+      <c r="AA29" s="134"/>
+      <c r="AB29" s="134"/>
+      <c r="AC29" s="134"/>
+      <c r="AD29" s="134"/>
+      <c r="AE29" s="134"/>
+      <c r="AF29" s="134"/>
+      <c r="AG29" s="134"/>
+      <c r="AH29" s="134"/>
+    </row>
+    <row r="30" spans="4:34" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D30" s="134" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="134"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="134"/>
+      <c r="J30" s="134"/>
+      <c r="K30" s="134"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="134"/>
+      <c r="N30" s="134"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="134"/>
+      <c r="Q30" s="134"/>
+      <c r="R30" s="134"/>
+      <c r="S30" s="134"/>
+      <c r="T30" s="134"/>
+      <c r="U30" s="134"/>
+      <c r="V30" s="134"/>
+      <c r="W30" s="134"/>
+      <c r="X30" s="134"/>
+      <c r="Y30" s="134"/>
+      <c r="Z30" s="134"/>
+      <c r="AA30" s="134"/>
+      <c r="AB30" s="134"/>
+      <c r="AC30" s="134"/>
+      <c r="AD30" s="134"/>
+      <c r="AE30" s="134"/>
+      <c r="AF30" s="134"/>
+      <c r="AG30" s="134"/>
+      <c r="AH30" s="134"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AJ4:AK4"/>
+  <mergeCells count="37">
+    <mergeCell ref="D30:AH30"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="AG26:AH26"/>
+    <mergeCell ref="D29:AH29"/>
+    <mergeCell ref="B2:AQ2"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="AA26:AB26"/>
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
@@ -14615,6 +15979,313 @@
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="V4:W4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AJ4:AK4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992DC469-7915-41D9-94F0-DE3877BBFA7C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D70B47BC-EAD3-4282-A715-EC279BD1A288}">
+  <dimension ref="B2:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="45.140625" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="126" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="126" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="126" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="126" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" s="126" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="126" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="127" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="127" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" s="128" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="127" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="128" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="129" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="132">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="127" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="127" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="128" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="127" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="128" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="129" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="130"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="127" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="128" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="128" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="129" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="130"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="127" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="127" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="128" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="128" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="129" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="132">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="127" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="128" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" s="128" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="129" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="130"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="127" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="127" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="128" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="128" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" s="129" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="127" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="128" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16" s="128" t="s">
+        <v>167</v>
+      </c>
+      <c r="G16" s="129" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="132">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
